--- a/data/trans_orig/IP31KM14_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP31KM14_2023-Edad-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6566</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3765</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>10695</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>17,54%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>10,06%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>28,57%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>4102</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1758</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>7814</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>8,82%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>3,78%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>16,81%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>7803</t>
+          <t>3737</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4322</t>
+          <t>1366</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12161</t>
+          <t>7021</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>10303</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7791</t>
+          <t>6588</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18073</t>
+          <t>15579</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>19,45%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>30869</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>26740</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>33670</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>82,46%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>71,43%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>89,94%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>76</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>42393</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>38681</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>44737</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>91,18%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>83,19%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>96,22%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>37482</t>
+          <t>38944</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>33124</t>
+          <t>35660</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>40963</t>
+          <t>41315</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>82,77%</t>
+          <t>91,24%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,15%</t>
+          <t>83,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,46%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>79875</t>
+          <t>69813</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>73706</t>
+          <t>64537</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>83988</t>
+          <t>73528</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>87,03%</t>
+          <t>87,14%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,31%</t>
+          <t>80,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>91,78%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>37435</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>37435</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>37435</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>46495</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>46495</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>46495</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>45285</t>
+          <t>42681</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>45285</t>
+          <t>42681</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>45285</t>
+          <t>42681</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>91779</t>
+          <t>80116</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>91779</t>
+          <t>80116</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>91779</t>
+          <t>80116</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>29576</t>
+          <t>28877</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21402</t>
+          <t>21894</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>37394</t>
+          <t>37496</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>32929</t>
+          <t>27569</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25139</t>
+          <t>20697</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>42556</t>
+          <t>35571</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>62505</t>
+          <t>56446</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>51001</t>
+          <t>46115</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>74408</t>
+          <t>66802</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>22,08%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>128165</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>119546</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>135148</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>81,61%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>76,12%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>86,06%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>209</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>129723</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>121905</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>137897</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>81,43%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>76,53%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>86,57%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>226</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>149030</t>
+          <t>117949</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>139403</t>
+          <t>109947</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>156820</t>
+          <t>124821</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>81,9%</t>
+          <t>81,05%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,61%</t>
+          <t>75,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,18%</t>
+          <t>85,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>278754</t>
+          <t>246114</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>266851</t>
+          <t>235758</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>290258</t>
+          <t>256445</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>81,68%</t>
+          <t>81,34%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,2%</t>
+          <t>77,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,06%</t>
+          <t>84,76%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>157042</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>157042</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>157042</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>275</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>181959</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>181959</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>181959</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>341259</t>
+          <t>302560</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>341259</t>
+          <t>302560</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>341259</t>
+          <t>302560</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>40632</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>30300</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>52330</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>20,3%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>15,14%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>26,15%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>33875</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>25842</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>45556</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>19,57%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>14,93%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>26,32%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>43164</t>
+          <t>32645</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>32583</t>
+          <t>24152</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>55342</t>
+          <t>42544</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>77039</t>
+          <t>73278</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>62906</t>
+          <t>60649</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>93841</t>
+          <t>87847</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>23,44%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>159494</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>147796</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>169826</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>79,7%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>73,85%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>84,86%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>189</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>139197</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>127516</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>147230</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>80,43%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>73,68%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>85,07%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>169326</t>
+          <t>142027</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>157148</t>
+          <t>132128</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>179907</t>
+          <t>150520</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>79,69%</t>
+          <t>81,31%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>73,96%</t>
+          <t>75,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,67%</t>
+          <t>86,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>308524</t>
+          <t>301520</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>291722</t>
+          <t>286951</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>322657</t>
+          <t>314149</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>80,02%</t>
+          <t>80,45%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>75,66%</t>
+          <t>76,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,68%</t>
+          <t>83,82%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>233</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>46628</t>
+          <t>51780</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30653</t>
+          <t>39010</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>60205</t>
+          <t>65378</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>57315</t>
+          <t>48244</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>42463</t>
+          <t>37683</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>75932</t>
+          <t>61438</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>103943</t>
+          <t>100024</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>83660</t>
+          <t>83566</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>127732</t>
+          <t>119068</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>21,75%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>227639</t>
+          <t>240441</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>214062</t>
+          <t>226843</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>243614</t>
+          <t>253211</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>83,0%</t>
+          <t>82,28%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,05%</t>
+          <t>77,63%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,82%</t>
+          <t>86,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>247684</t>
+          <t>207093</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>229067</t>
+          <t>193899</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>262536</t>
+          <t>217654</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>81,21%</t>
+          <t>81,11%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,1%</t>
+          <t>75,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,08%</t>
+          <t>85,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>475323</t>
+          <t>447534</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>451534</t>
+          <t>428490</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>495606</t>
+          <t>463992</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>82,06%</t>
+          <t>81,73%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,95%</t>
+          <t>78,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,56%</t>
+          <t>84,74%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>274267</t>
+          <t>292221</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>274267</t>
+          <t>292221</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>274267</t>
+          <t>292221</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>304999</t>
+          <t>255337</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>304999</t>
+          <t>255337</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>304999</t>
+          <t>255337</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>579266</t>
+          <t>547558</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>579266</t>
+          <t>547558</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>579266</t>
+          <t>547558</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>127855</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>110698</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>148862</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>18,62%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>16,12%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>21,67%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>157</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>114180</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>94435</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>134058</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>17,48%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>14,46%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>20,53%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>141210</t>
+          <t>112195</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>120956</t>
+          <t>95356</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>168997</t>
+          <t>129370</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>255390</t>
+          <t>240050</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>226784</t>
+          <t>215056</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>288156</t>
+          <t>265890</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>20,37%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>773</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>558969</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>537962</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>576126</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>81,38%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>78,33%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>83,88%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>758</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>538954</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>519076</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>558699</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>82,52%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>79,47%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>85,54%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>773</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>603523</t>
+          <t>506013</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>575736</t>
+          <t>488838</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>623777</t>
+          <t>522852</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>81,04%</t>
+          <t>81,85%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,31%</t>
+          <t>79,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>84,58%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1142477</t>
+          <t>1064981</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1109711</t>
+          <t>1039141</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1171083</t>
+          <t>1089975</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>81,73%</t>
+          <t>81,61%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>79,39%</t>
+          <t>79,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>83,78%</t>
+          <t>83,52%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>915</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>940</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
